--- a/data/processed/positivacao/2025-03_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2025-03_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26765,7 +26765,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr"/>
@@ -37909,7 +37909,7 @@
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr"/>
@@ -66047,7 +66047,7 @@
     <row r="2529">
       <c r="A2529" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2529" t="inlineStr"/>
@@ -67718,12 +67718,12 @@
       <c r="A2594" t="inlineStr"/>
       <c r="B2594" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 6 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 5.070,01
+          <t>Vendedor 1 - VENDEDOR 01: positivou 6 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 5.070,01
 Vendedor 18 - LOJA: positivou 242 cliente(s), não positivou 672 cliente(s) - Total vendido: R$ 91.336,52
-Vendedor 3 - FERNANDA: positivou 110 cliente(s), não positivou 318 cliente(s) - Total vendido: R$ 166.022,53
-Vendedor 4 - DANIELA: positivou 116 cliente(s), não positivou 521 cliente(s) - Total vendido: R$ 68.930,97
+Vendedor 3 - VENDEDOR 03: positivou 110 cliente(s), não positivou 318 cliente(s) - Total vendido: R$ 166.022,53
+Vendedor 4 - VENDEDOR 04: positivou 116 cliente(s), não positivou 521 cliente(s) - Total vendido: R$ 68.930,97
 Vendedor 5 - SITE: positivou 3 cliente(s), não positivou 441 cliente(s) - Total vendido: R$ 1.008,82
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2594" t="inlineStr"/>
